--- a/data/reference/battery_energy_capacity.xlsx
+++ b/data/reference/battery_energy_capacity.xlsx
@@ -581,12 +581,32 @@
           <t>LS25 5JB</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
+      <c r="N2" t="n">
+        <v>640</v>
+      </c>
+      <c r="O2" t="n">
+        <v>2</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>corporate</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>https://www.sserenewables.com/</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>SSE press release</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -626,12 +646,32 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
+      <c r="N3" t="n">
+        <v>600</v>
+      </c>
+      <c r="O3" t="n">
+        <v>2</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>corporate</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>https://stateraenergy.co.uk/</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>Statera Energy Thurrock Storage</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -689,12 +729,32 @@
           <t>BS35 3TF</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
+      <c r="N4" t="n">
+        <v>300</v>
+      </c>
+      <c r="O4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>corporate</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>https://constantineenergystorage.com/</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>Constantine portfolio</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -752,12 +812,32 @@
           <t>DN40 3BH</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr"/>
+      <c r="N5" t="n">
+        <v>160</v>
+      </c>
+      <c r="O5" t="n">
+        <v>2</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>corporate</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>https://conradenergy.co.uk/</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>Conrad Energy for KX Power</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -842,12 +922,32 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
+      <c r="N7" t="n">
+        <v>114</v>
+      </c>
+      <c r="O7" t="n">
+        <v>2</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>corporate</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>https://www.edfenergy.com/</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>EDF / Pivot Power (Bramford)</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -950,12 +1050,32 @@
           <t xml:space="preserve">SA1 8NS </t>
         </is>
       </c>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr"/>
-      <c r="S9" t="inlineStr"/>
+      <c r="N9" t="n">
+        <v>137.5</v>
+      </c>
+      <c r="O9" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>corporate</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>https://chamberscapital.co.uk/</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>Varco Energy / Ethical Power</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1143,12 +1263,32 @@
           <t>CH66 2HD</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="inlineStr"/>
-      <c r="S12" t="inlineStr"/>
+      <c r="N12" t="n">
+        <v>138</v>
+      </c>
+      <c r="O12" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>corporate</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>https://jpsil.co.uk/</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>Varco Energy / Adaptogen (Mersey Ring)</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1206,12 +1346,32 @@
           <t>WV3 8EA</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr"/>
-      <c r="S13" t="inlineStr"/>
+      <c r="N13" t="n">
+        <v>310</v>
+      </c>
+      <c r="O13" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>corporate</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>https://www.prnewswire.com/</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>Envision &amp; Pulse Clean Energy</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1273,12 +1433,32 @@
           <t>WS5 4RA</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="inlineStr"/>
-      <c r="S14" t="inlineStr"/>
+      <c r="N14" t="n">
+        <v>100</v>
+      </c>
+      <c r="O14" t="n">
+        <v>2</v>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>corporate</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>https://www.wartsila.com/</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>Wartsila / EDF delivery</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">

--- a/data/reference/battery_energy_capacity.xlsx
+++ b/data/reference/battery_energy_capacity.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S46"/>
+  <dimension ref="A1:W65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -524,6 +524,26 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>task</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>current_mwh</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>current_source</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>current_implied_h</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -607,6 +627,10 @@
           <t>SSE press release</t>
         </is>
       </c>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -672,6 +696,10 @@
           <t>Statera Energy Thurrock Storage</t>
         </is>
       </c>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -755,6 +783,10 @@
           <t>Constantine portfolio</t>
         </is>
       </c>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -838,30 +870,34 @@
           <t>Conrad Energy for KX Power</t>
         </is>
       </c>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>GB-BESS-WBURB</t>
+          <t>GB-BESS-TYLNB</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>West Burton B Battery</t>
+          <t>Tye Lane BESS</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>West Burton B Limited</t>
+          <t>Pivoted Power LLP</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>T_WBURB-41, T_WBURB-43</t>
+          <t>T_TYLNB-1</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>62</v>
+        <v>59.2</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -877,36 +913,60 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr"/>
+      <c r="N6" t="n">
+        <v>114</v>
+      </c>
+      <c r="O6" t="n">
+        <v>2</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>corporate</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>https://www.edfenergy.com/</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>EDF / Pivot Power (Bramford)</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>GB-BESS-TYLNB</t>
+          <t>GB-BESS-SZJNB</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Tye Lane BESS</t>
+          <t>Sizing John</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Pivoted Power LLP</t>
+          <t>Arenko Cleantech Limited</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>T_TYLNB-1</t>
+          <t>T_SZJNB-1</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>59.2</v>
+        <v>57</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -916,17 +976,35 @@
       <c r="G7" t="b">
         <v>0</v>
       </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>John Green Frog Power Compound, John North Road - Battery System</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Green Frog Power Limited</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>20</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Awaiting Construction</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SA1 8NS </t>
+        </is>
+      </c>
       <c r="N7" t="n">
-        <v>114</v>
+        <v>137.5</v>
       </c>
       <c r="O7" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
@@ -935,7 +1013,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>https://www.edfenergy.com/</t>
+          <t>https://chamberscapital.co.uk/</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -945,33 +1023,37 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>EDF / Pivot Power (Bramford)</t>
-        </is>
-      </c>
+          <t>Varco Energy / Ethical Power</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>GB-BESS-OCHLB</t>
+          <t>GB-BESS-NTRVB</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Ocker Hill</t>
+          <t>Native River</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>HD143OCK Ltd</t>
+          <t>Arenko Cleantech Limited</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>T_OCHLB-1</t>
+          <t>T_NTRVB-1</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -981,46 +1063,92 @@
       <c r="G8" t="b">
         <v>0</v>
       </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Native River</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Varco Energy</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>57</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Operational</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>14/04/2025</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>CH66 2HD</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
+        <v>138</v>
+      </c>
+      <c r="O8" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>corporate</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>https://jpsil.co.uk/</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>Varco Energy / Adaptogen (Mersey Ring)</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>GB-BESS-SZJNB</t>
+          <t>GB-BESS-WOLVB</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Sizing John</t>
+          <t>Wolverhampton West BESS</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Arenko Cleantech Limited</t>
+          <t>EDF Energy Customers Limited</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>T_SZJNB-1</t>
+          <t>E_WOLVB-1</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Transmission</t>
+          <t>Distribution</t>
         </is>
       </c>
       <c r="G9" t="b">
@@ -1028,30 +1156,30 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>John Green Frog Power Compound, John North Road - Battery System</t>
+          <t>Wolverhampton West Sub Station</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Green Frog Power Limited</t>
+          <t>Statera Energy</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Awaiting Construction</t>
+          <t>Planning Permission Expired</t>
         </is>
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t xml:space="preserve">SA1 8NS </t>
+          <t>WV3 8EA</t>
         </is>
       </c>
       <c r="N9" t="n">
-        <v>137.5</v>
+        <v>310</v>
       </c>
       <c r="O9" t="n">
         <v>2.4</v>
@@ -1063,7 +1191,7 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>https://chamberscapital.co.uk/</t>
+          <t>https://www.prnewswire.com/</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -1073,33 +1201,37 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>Varco Energy / Ethical Power</t>
-        </is>
-      </c>
+          <t>Envision &amp; Pulse Clean Energy</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>GB-BESS-MKFRB</t>
+          <t>GB-BESS-BUSTB</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Monk Fryston</t>
+          <t>Pivot Power Bustleholme</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>HD777FRY Ltd</t>
+          <t>Pivoted Power LLP</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>T_MKFRB-1</t>
+          <t>T_BUSTB-1</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>57</v>
+        <v>52.2</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1111,58 +1243,86 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Monk Fryston Battery Storage</t>
+          <t>Bustleholme Substation</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Pelagic Energy / Constantine</t>
+          <t>Pivot Power</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>57</v>
+        <v>49.9</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Under Construction</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr"/>
+          <t>Operational</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>20/10/2023</t>
+        </is>
+      </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>LS25 5LD</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr"/>
-      <c r="S10" t="inlineStr"/>
+          <t>WS5 4RA</t>
+        </is>
+      </c>
+      <c r="N10" t="n">
+        <v>100</v>
+      </c>
+      <c r="O10" t="n">
+        <v>2</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>corporate</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>https://www.wartsila.com/</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>Wartsila / EDF delivery</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>GB-BESS-CAPNB</t>
+          <t>GB-BESS-COWB</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Capenhurst</t>
+          <t>Cowley</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>HD888CAP Ltd</t>
+          <t>Pivoted Power LLP</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>T_CAPNB-1</t>
+          <t>T_COWB-1</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>57</v>
+        <v>50.4</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1174,100 +1334,106 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Capenhurst Lane, Capenhurst - Battery storage</t>
+          <t>Cowley electricity sub-station</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>HD888CAP Limited</t>
+          <t>Pivot Power</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>57</v>
+        <v>49.9</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Under Construction</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr"/>
+          <t>Operational</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>22/06/2021</t>
+        </is>
+      </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>CH1 6EH</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr"/>
-      <c r="S11" t="inlineStr"/>
+          <t>OX44 9BD</t>
+        </is>
+      </c>
+      <c r="N11" t="n">
+        <v>50</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>corporate</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>https://www.wartsila.com/</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>Energy Superhub Oxford (Pivot Power / Wartsila)</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>GB-BESS-NTRVB</t>
+          <t>GB-BESS-CATHB</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Native River</t>
+          <t>CathkinBattery</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Arenko Cleantech Limited</t>
+          <t>ENGIE Power Limited</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>T_NTRVB-1</t>
+          <t>E_CATHB-1</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>57</v>
+        <v>49.9</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Transmission</t>
+          <t>Distribution</t>
         </is>
       </c>
       <c r="G12" t="b">
         <v>0</v>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Native River</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>Varco Energy</t>
-        </is>
-      </c>
-      <c r="J12" t="n">
-        <v>57</v>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>Operational</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>14/04/2025</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>CH66 2HD</t>
-        </is>
-      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
       <c r="N12" t="n">
-        <v>138</v>
+        <v>100</v>
       </c>
       <c r="O12" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="P12" t="inlineStr">
         <is>
@@ -1276,7 +1442,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>https://jpsil.co.uk/</t>
+          <t>https://www.energyglobal.com/</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1286,33 +1452,37 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>Varco Energy / Adaptogen (Mersey Ring)</t>
-        </is>
-      </c>
+          <t>ENGIE &amp; Canadian Solar e-STORAGE</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>GB-BESS-WOLVB</t>
+          <t>GB-BESS-SKELB</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Wolverhampton West BESS</t>
+          <t>Skelmersdale Battery</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>EDF Energy Customers Limited</t>
+          <t>Tesla Motors Limited</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>E_WOLVB-1</t>
+          <t>E_SKELB-1</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>56</v>
+        <v>49.9</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1322,35 +1492,17 @@
       <c r="G13" t="b">
         <v>0</v>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Wolverhampton West Sub Station</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>Statera Energy</t>
-        </is>
-      </c>
-      <c r="J13" t="n">
-        <v>50</v>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>Planning Permission Expired</t>
-        </is>
-      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>WV3 8EA</t>
-        </is>
-      </c>
+      <c r="M13" t="inlineStr"/>
       <c r="N13" t="n">
-        <v>310</v>
+        <v>99.8</v>
       </c>
       <c r="O13" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="P13" t="inlineStr">
         <is>
@@ -1359,7 +1511,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>https://www.prnewswire.com/</t>
+          <t>https://www.amberinfrastructure.com/</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -1369,19 +1521,23 @@
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>Envision &amp; Pulse Clean Energy</t>
-        </is>
-      </c>
+          <t>Amber Infrastructure &amp; Tesla</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>GB-BESS-BUSTB</t>
+          <t>GB-BESS-INDQB</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Pivot Power Bustleholme</t>
+          <t>INDIAN QUEENS BESS</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1391,11 +1547,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>T_BUSTB-1</t>
+          <t>T_INDQB-1</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>52.2</v>
+        <v>47.5</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1407,34 +1563,30 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Bustleholme Substation</t>
+          <t>Indian Queens Sub-Station - Battery Storage</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Pivot Power</t>
+          <t>Prime Energy Development Limited / Valero Energy / Sambar Power</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>49.9</v>
+        <v>47.5</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Operational</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>20/10/2023</t>
-        </is>
-      </c>
+          <t>Awaiting Construction</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>WS5 4RA</t>
+          <t>PL26 8BY</t>
         </is>
       </c>
       <c r="N14" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="O14" t="n">
         <v>2</v>
@@ -1446,7 +1598,7 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>https://www.wartsila.com/</t>
+          <t>https://www.edfenergy.com/</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
@@ -1456,78 +1608,128 @@
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>Wartsila / EDF delivery</t>
-        </is>
-      </c>
+          <t>EDF Renewables / Pivot Power</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>GB-BESS-HRSTB</t>
+          <t>GB-BESS-CRSSB</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>T_HRSTB-1</t>
+          <t>Carnegie Road 1</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>SP Renewables (UK) Limited</t>
+          <t>Arenko Cleantech Limited</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>T_HRSTB-1</t>
+          <t>E_CRSSB-1</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>52</v>
+        <v>20</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Transmission</t>
+          <t>Distribution</t>
         </is>
       </c>
       <c r="G15" t="b">
         <v>0</v>
       </c>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr"/>
-      <c r="S15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Land at Carnegie Road</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Ørsted</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>20</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Operational</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>24/12/2018</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>L13 7HY</t>
+        </is>
+      </c>
+      <c r="N15" t="n">
+        <v>20</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1</v>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>corporate</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>https://www.favershamsociety.org/</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>Orsted / NEC Energy Solutions</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>GB-BESS-COWB</t>
+          <t>GB-BESS-LKSDB</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Cowley</t>
+          <t>Lakeside  BESS</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Pivoted Power LLP</t>
+          <t>Lakeside Energy Storage Ltd</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>T_COWB-1</t>
+          <t>T_LKSDB-1</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>50.4</v>
+        <v>105</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1539,30 +1741,26 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Cowley electricity sub-station</t>
+          <t>Lakeside Energy Storage Facility</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Pivot Power</t>
+          <t>Tag Energy UK</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>49.9</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Operational</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>22/06/2021</t>
-        </is>
-      </c>
+          <t>Awaiting Construction</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>OX44 9BD</t>
+          <t>YO8 8FP</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -1571,75 +1769,125 @@
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>verify</t>
+        </is>
+      </c>
+      <c r="U16" t="n">
+        <v>149.9</v>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>capacity_market</t>
+        </is>
+      </c>
+      <c r="W16" t="n">
+        <v>1.43</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>GB-BESS-CATHB</t>
+          <t>GB-BESS-BRETB</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CathkinBattery</t>
+          <t>Brentwood BESS</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ENGIE Power Limited</t>
+          <t>EDF Energy Customers Limited</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>E_CATHB-1</t>
+          <t>E_BRETB-1, E_BRETB-2</t>
         </is>
       </c>
       <c r="E17" t="n">
+        <v>104</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Distribution</t>
+        </is>
+      </c>
+      <c r="G17" t="b">
+        <v>0</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Brentwood nergy Storage System</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Anesco Limited</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
         <v>49.9</v>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Distribution</t>
-        </is>
-      </c>
-      <c r="G17" t="b">
-        <v>0</v>
-      </c>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Awaiting Construction</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>CM13</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr"/>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>verify</t>
+        </is>
+      </c>
+      <c r="U17" t="n">
+        <v>49.9</v>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>capacity_market</t>
+        </is>
+      </c>
+      <c r="W17" t="n">
+        <v>0.48</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>GB-BESS-SKELB</t>
+          <t>GB-BESS-BERKB</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Skelmersdale Battery</t>
+          <t>Berkeley BESS</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Tesla Motors Limited</t>
+          <t>EDF Energy Customers Limited</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>E_SKELB-1</t>
+          <t>E_BERKB-1, E_BERKB-2</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>49.9</v>
+        <v>104</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1661,34 +1909,50 @@
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>verify</t>
+        </is>
+      </c>
+      <c r="U18" t="n">
+        <v>49.9</v>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>capacity_market</t>
+        </is>
+      </c>
+      <c r="W18" t="n">
+        <v>0.48</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>GB-BESS-THMRB</t>
+          <t>GB-BESS-WBURB</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Thame Road  BESS</t>
+          <t>West Burton B Battery</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Tesla Motors Limited</t>
+          <t>West Burton B Limited</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>E_THMRB-1</t>
+          <t>T_WBURB-41, T_WBURB-43</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>49.5</v>
+        <v>62</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Distribution</t>
+          <t>Transmission</t>
         </is>
       </c>
       <c r="G19" t="b">
@@ -1706,34 +1970,42 @@
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>fill</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="inlineStr"/>
+      <c r="W19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>GB-BESS-ILMEB</t>
+          <t>GB-BESS-OCHLB</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Ilmer Lane BESS</t>
+          <t>Ocker Hill</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Tesla Motors Limited</t>
+          <t>HD143OCK Ltd</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>E_ILMEB-1</t>
+          <t>T_OCHLB-1</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>49.5</v>
+        <v>58</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Distribution</t>
+          <t>Transmission</t>
         </is>
       </c>
       <c r="G20" t="b">
@@ -1751,79 +2023,121 @@
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="inlineStr"/>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>fill</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="inlineStr"/>
+      <c r="W20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>GB-BESS-JAMBB</t>
+          <t>GB-BESS-WTGTB</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Jamesfield 1 Battery Storage</t>
+          <t>Whitegate</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Tesla Motors Limited</t>
+          <t>HD144WHI Ltd</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>E_JAMBB-1, E_JAMBB-2</t>
+          <t>T_WTGTB-1</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Distribution</t>
+          <t>Transmission</t>
         </is>
       </c>
       <c r="G21" t="b">
         <v>0</v>
       </c>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Whitegate Battery Storage</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Pelagic Energy (Constantine Energy)</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>57</v>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Under Construction</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>OL9 9XA</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr"/>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr"/>
       <c r="S21" t="inlineStr"/>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>verify</t>
+        </is>
+      </c>
+      <c r="U21" t="n">
+        <v>114</v>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>capacity_market</t>
+        </is>
+      </c>
+      <c r="W21" t="n">
+        <v>1.97</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>GB-BESS-TOLLB</t>
+          <t>GB-BESS-MKFRB</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Tollgate Energy Storage</t>
+          <t>Monk Fryston</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Tollgate Energy Storage Ltd</t>
+          <t>HD777FRY Ltd</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>E_TOLLB-1</t>
+          <t>T_MKFRB-1</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Distribution</t>
+          <t>Transmission</t>
         </is>
       </c>
       <c r="G22" t="b">
@@ -1831,26 +2145,26 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Tollgate Battery Storage Facility</t>
+          <t>Monk Fryston Battery Storage</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>RNA Energy</t>
+          <t>Pelagic Energy / Constantine</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>49.5</v>
+        <v>57</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Revised</t>
+          <t>Under Construction</t>
         </is>
       </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>AL4 0NY</t>
+          <t>LS25 5LD</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -1859,30 +2173,38 @@
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr"/>
       <c r="S22" t="inlineStr"/>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>fill</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr"/>
+      <c r="V22" t="inlineStr"/>
+      <c r="W22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>GB-BESS-NURSB</t>
+          <t>GB-BESS-CAPNB</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Nursling Battery Storage</t>
+          <t>Capenhurst</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>EDF Energy Customers Limited</t>
+          <t>HD888CAP Ltd</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>T_NURSB-1</t>
+          <t>T_CAPNB-1</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1894,26 +2216,26 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Upton Lane, Nursling - Battery Storage Facility</t>
+          <t>Capenhurst Lane, Capenhurst - Battery storage</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>HD888CAP Limited</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Awaiting Construction</t>
+          <t>Under Construction</t>
         </is>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>SO16 0XY</t>
+          <t>CH1 6EH</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
@@ -1922,30 +2244,38 @@
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr"/>
       <c r="S23" t="inlineStr"/>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>fill</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr"/>
+      <c r="V23" t="inlineStr"/>
+      <c r="W23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>GB-BESS-INDQB</t>
+          <t>GB-BESS-BLPFB</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>INDIAN QUEENS BESS</t>
+          <t>Bulphan Fen Warley Green BESS</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Pivoted Power LLP</t>
+          <t>EDF Energy Customers Limited</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>T_INDQB-1</t>
+          <t>T_BLPFB-1</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>47.5</v>
+        <v>56.6</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1957,26 +2287,24 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Indian Queens Sub-Station - Battery Storage</t>
+          <t>Bulphan Fen Solar Farm &amp; Battery Storage</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Prime Energy Development Limited / Valero Energy / Sambar Power</t>
-        </is>
-      </c>
-      <c r="J24" t="n">
-        <v>47.5</v>
-      </c>
+          <t>Warley Green Limited</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Awaiting Construction</t>
+          <t>Under Construction</t>
         </is>
       </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>PL26 8BY</t>
+          <t>RM14 3RE</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
@@ -1985,34 +2313,50 @@
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr"/>
       <c r="S24" t="inlineStr"/>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>verify</t>
+        </is>
+      </c>
+      <c r="U24" t="n">
+        <v>75</v>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>capacity_market</t>
+        </is>
+      </c>
+      <c r="W24" t="n">
+        <v>1.32</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>GB-BESS-ARNKB</t>
+          <t>GB-BESS-HRSTB</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>AR0006-BLOX</t>
+          <t>T_HRSTB-1</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Octopus Energy Trading Limited</t>
+          <t>SP Renewables (UK) Limited</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>E_ARNKB-1</t>
+          <t>T_HRSTB-1</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>41.7</v>
+        <v>52</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Distribution</t>
+          <t>Transmission</t>
         </is>
       </c>
       <c r="G25" t="b">
@@ -2030,79 +2374,85 @@
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr"/>
       <c r="S25" t="inlineStr"/>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>fill</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr"/>
+      <c r="V25" t="inlineStr"/>
+      <c r="W25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>GB-BESS-FIDL</t>
+          <t>GB-BESS-BROFB</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Fiddler's Ferry 2</t>
+          <t>Brook Farm BESS</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Keadby Generation Limited</t>
+          <t>EDF Energy Customers Limited</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>T_FIDL-2, T_FIDL-3, T_FIDL-4</t>
+          <t>E_BROFB-1</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Transmission</t>
+          <t>Distribution</t>
         </is>
       </c>
       <c r="G26" t="b">
         <v>0</v>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Fiddlers Ferry Power Station - Battery storage</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>SSE Enterprise (SSE PLC)</t>
-        </is>
-      </c>
-      <c r="J26" t="n">
-        <v>150</v>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>Under Construction</t>
-        </is>
-      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>WA5 2UT</t>
-        </is>
-      </c>
+      <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr"/>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr"/>
       <c r="S26" t="inlineStr"/>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>verify</t>
+        </is>
+      </c>
+      <c r="U26" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>capacity_market</t>
+        </is>
+      </c>
+      <c r="W26" t="n">
+        <v>0.95</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>GB-BESS-KEMB</t>
+          <t>GB-BESS-NEWTB</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Pivot Power Kemsley</t>
+          <t>Newton wood BESS</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2112,82 +2462,76 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>T_KEMB-1</t>
+          <t>E_NEWTB-1</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>40.1</v>
+        <v>52</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Transmission</t>
+          <t>Distribution</t>
         </is>
       </c>
       <c r="G27" t="b">
         <v>0</v>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Kemsley Substation</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>Pivot Power</t>
-        </is>
-      </c>
-      <c r="J27" t="n">
-        <v>49.9</v>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>Operational</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>25/10/2021</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>ME10 2</t>
-        </is>
-      </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr"/>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr"/>
       <c r="S27" t="inlineStr"/>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>verify</t>
+        </is>
+      </c>
+      <c r="U27" t="n">
+        <v>49.9</v>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>capacity_market</t>
+        </is>
+      </c>
+      <c r="W27" t="n">
+        <v>0.96</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>GB-BESS-DALMB</t>
+          <t>GB-BESS-COVNB</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Dalmarnock_BESS</t>
+          <t>Pivot Power Coventry</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>EDF Energy Customers Limited</t>
+          <t>Pivoted Power LLP</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>E_DALMB-1</t>
+          <t>T_COVNB-1</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>40</v>
+        <v>50.4</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Distribution</t>
+          <t>Transmission</t>
         </is>
       </c>
       <c r="G28" t="b">
@@ -2195,26 +2539,30 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Dalmarnock Road - Battery Storage</t>
+          <t>Coventry National Grid Substation</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>EcoDev Group Limited</t>
+          <t>Pivot Power</t>
         </is>
       </c>
       <c r="J28" t="n">
-        <v>40</v>
+        <v>49.9</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Awaiting Construction</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr"/>
+          <t>Operational</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>01/12/2023</t>
+        </is>
+      </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>G73 1NY</t>
+          <t>CV2 1NQ</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
@@ -2223,30 +2571,46 @@
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr"/>
       <c r="S28" t="inlineStr"/>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>verify</t>
+        </is>
+      </c>
+      <c r="U28" t="n">
+        <v>80</v>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>capacity_market</t>
+        </is>
+      </c>
+      <c r="W28" t="n">
+        <v>1.59</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>GB-BESS-SHILB</t>
+          <t>GB-BESS-CHAPB</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Shilton Lane BESS</t>
+          <t>Chapel Farm BESS</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Octopus Energy Trading Limited</t>
+          <t>Tesla Motors Limited</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>E_SHILB-1</t>
+          <t>E_CHAPB-1</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>40</v>
+        <v>50.2</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2256,125 +2620,119 @@
       <c r="G29" t="b">
         <v>0</v>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Land SW of Shilton Cottage</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>Muirhall Energy</t>
-        </is>
-      </c>
-      <c r="J29" t="n">
-        <v>29.9</v>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>Operational</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>01/01/2022</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>PA7 5BB</t>
-        </is>
-      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="O29" t="inlineStr"/>
       <c r="P29" t="inlineStr"/>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr"/>
       <c r="S29" t="inlineStr"/>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>verify</t>
+        </is>
+      </c>
+      <c r="U29" t="n">
+        <v>84</v>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>capacity_market</t>
+        </is>
+      </c>
+      <c r="W29" t="n">
+        <v>1.67</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>GB-BESS-TEBWB</t>
+          <t>GB-BESS-LITRB</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Tebworth BESS Power Park</t>
+          <t>Little Raith BESS</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Arenko Cleantech Limited</t>
+          <t>Tesla Motors Limited</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>T_TEBWB-1</t>
+          <t>E_LITRB-1</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>39.9</v>
+        <v>50</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Transmission</t>
+          <t>Distribution</t>
         </is>
       </c>
       <c r="G30" t="b">
         <v>0</v>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Tebworth - Battery Storage</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>Sundon Green Limited</t>
-        </is>
-      </c>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>Under Construction</t>
-        </is>
-      </c>
+      <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>LU7 9BP</t>
-        </is>
-      </c>
+      <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr"/>
       <c r="P30" t="inlineStr"/>
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr"/>
       <c r="S30" t="inlineStr"/>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>verify</t>
+        </is>
+      </c>
+      <c r="U30" t="n">
+        <v>98</v>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>capacity_market</t>
+        </is>
+      </c>
+      <c r="W30" t="n">
+        <v>1.96</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>GB-BESS-POTES</t>
+          <t>GB-BESS-ROARB</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Port of Tyne Energy Storage</t>
+          <t>Roaring Hill BESS</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Arenko Cleantech Limited</t>
+          <t>Tesla Motors Limited</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>E_POTES-1</t>
+          <t>E_ROARB-1</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2386,30 +2744,26 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Port of Tyne</t>
+          <t>Roaring Hill (Resubmission)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Foresight</t>
+          <t>Renewable Energy Systems (RES)</t>
         </is>
       </c>
       <c r="J31" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>Operational</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>01/07/2018</t>
-        </is>
-      </c>
+          <t>Revised</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>NE34 9PT</t>
+          <t>KY6 3ET</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
@@ -2418,34 +2772,50 @@
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr"/>
       <c r="S31" t="inlineStr"/>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>verify</t>
+        </is>
+      </c>
+      <c r="U31" t="n">
+        <v>75</v>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>capacity_market</t>
+        </is>
+      </c>
+      <c r="W31" t="n">
+        <v>1.5</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>GB-BESS-ARBRB</t>
+          <t>GB-BESS-NLSTB</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Arbroath Battery Storage</t>
+          <t>Neilston Battery 1</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Octopus Energy Trading Limited</t>
+          <t>Statkraft Markets Gmbh</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>E_ARBRB-1</t>
+          <t>T_NLSTB-1</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>34.5</v>
+        <v>50</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Distribution</t>
+          <t>Transmission</t>
         </is>
       </c>
       <c r="G32" t="b">
@@ -2453,30 +2823,26 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Arbroath Battery Storage</t>
+          <t>Neilston  Greener Grid Park</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Coronation Power / Persimmon Homes</t>
+          <t>Statkraft UK LTD</t>
         </is>
       </c>
       <c r="J32" t="n">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>Operational</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>02/04/2024</t>
-        </is>
-      </c>
+          <t>Under Construction</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>DD11 3ET</t>
+          <t>PA1</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
@@ -2485,75 +2851,125 @@
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr"/>
       <c r="S32" t="inlineStr"/>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>verify</t>
+        </is>
+      </c>
+      <c r="U32" t="n">
+        <v>110.7</v>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>capacity_market</t>
+        </is>
+      </c>
+      <c r="W32" t="n">
+        <v>2.21</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>GB-BESS-BLKPB</t>
+          <t>GB-BESS-COYLB</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Coylton  Greener Grid  Park</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Conrad Energy (Trading) Ltd</t>
+          <t>Statkraft Markets Gmbh</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>E_BLKPB-1</t>
+          <t>T_COYLB-1</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>25.3</v>
+        <v>50</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Distribution</t>
+          <t>Transmission</t>
         </is>
       </c>
       <c r="G33" t="b">
         <v>0</v>
       </c>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Coylton Substation, Coylton - Battery Energy Storage</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Statkraft UK Limited</t>
+        </is>
+      </c>
+      <c r="J33" t="n">
+        <v>50</v>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Under Construction</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>KA18 2RN</t>
+        </is>
+      </c>
       <c r="N33" t="inlineStr"/>
       <c r="O33" t="inlineStr"/>
       <c r="P33" t="inlineStr"/>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr"/>
       <c r="S33" t="inlineStr"/>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>verify</t>
+        </is>
+      </c>
+      <c r="U33" t="n">
+        <v>59.8</v>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>capacity_market</t>
+        </is>
+      </c>
+      <c r="W33" t="n">
+        <v>1.2</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>GB-BESS-TORQB</t>
+          <t>GB-BESS-THMRB</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Torquay</t>
+          <t>Thame Road  BESS</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Conrad Energy (Trading) Ltd</t>
+          <t>Tesla Motors Limited</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>E_TORQB-1</t>
+          <t>E_THMRB-1</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>22.4</v>
+        <v>49.5</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2575,97 +2991,91 @@
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr"/>
       <c r="S34" t="inlineStr"/>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>fill</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr"/>
+      <c r="V34" t="inlineStr"/>
+      <c r="W34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>GB-BESS-PNYCB</t>
+          <t>GB-BESS-ILMEB</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Pen y Cymoedd Battery</t>
+          <t>Ilmer Lane BESS</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Arenko Cleantech Limited</t>
+          <t>Tesla Motors Limited</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>T_PNYCB-1</t>
+          <t>E_ILMEB-1</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>22</v>
+        <v>49.5</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Transmission</t>
+          <t>Distribution</t>
         </is>
       </c>
       <c r="G35" t="b">
         <v>0</v>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Pen y Cymoedd Energy Storage</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>Vattenfall</t>
-        </is>
-      </c>
-      <c r="J35" t="n">
-        <v>22</v>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>Operational</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>01/05/2018</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>SA13 3HF</t>
-        </is>
-      </c>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="O35" t="inlineStr"/>
       <c r="P35" t="inlineStr"/>
       <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr"/>
       <c r="S35" t="inlineStr"/>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>fill</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr"/>
+      <c r="V35" t="inlineStr"/>
+      <c r="W35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>GB-BESS-NEWPB</t>
+          <t>GB-BESS-JAMBB</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Newport BESS</t>
+          <t>Jamesfield 1 Battery Storage</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Field Newport Ltd</t>
+          <t>Tesla Motors Limited</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>E_NEWPB-1</t>
+          <t>E_JAMBB-1, E_JAMBB-2</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>20.9</v>
+        <v>49</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2687,30 +3097,38 @@
       <c r="Q36" t="inlineStr"/>
       <c r="R36" t="inlineStr"/>
       <c r="S36" t="inlineStr"/>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>fill</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr"/>
+      <c r="V36" t="inlineStr"/>
+      <c r="W36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>GB-BESS-CRSSB</t>
+          <t>GB-BESS-TOLLB</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Carnegie Road 1</t>
+          <t>Tollgate Energy Storage</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Arenko Cleantech Limited</t>
+          <t>Tollgate Energy Storage Ltd</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>E_CRSSB-1</t>
+          <t>E_TOLLB-1</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>20</v>
+        <v>49</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2722,30 +3140,26 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Land at Carnegie Road</t>
+          <t>Tollgate Battery Storage Facility</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Ørsted</t>
+          <t>RNA Energy</t>
         </is>
       </c>
       <c r="J37" t="n">
-        <v>20</v>
+        <v>49.5</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>Operational</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>24/12/2018</t>
-        </is>
-      </c>
+          <t>Revised</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>L13 7HY</t>
+          <t>AL4 0NY</t>
         </is>
       </c>
       <c r="N37" t="inlineStr"/>
@@ -2754,75 +3168,109 @@
       <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr"/>
       <c r="S37" t="inlineStr"/>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>fill</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr"/>
+      <c r="V37" t="inlineStr"/>
+      <c r="W37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>GB-BESS-HAWKB</t>
+          <t>GB-BESS-NURSB</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>HawkersHill  Battery</t>
+          <t>Nursling Battery Storage</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Tesla Motors Limited</t>
+          <t>EDF Energy Customers Limited</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>E_HAWKB-1</t>
+          <t>T_NURSB-1</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Distribution</t>
+          <t>Transmission</t>
         </is>
       </c>
       <c r="G38" t="b">
         <v>0</v>
       </c>
-      <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Upton Lane, Nursling - Battery Storage Facility</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J38" t="n">
+        <v>50</v>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Awaiting Construction</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>SO16 0XY</t>
+        </is>
+      </c>
       <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr"/>
       <c r="P38" t="inlineStr"/>
       <c r="Q38" t="inlineStr"/>
       <c r="R38" t="inlineStr"/>
       <c r="S38" t="inlineStr"/>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>fill</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr"/>
+      <c r="V38" t="inlineStr"/>
+      <c r="W38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>GB-BESS-GRCRB</t>
+          <t>GB-BESS-BARNB</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Gerrards Cross BESS</t>
+          <t>Hunningley Stairfoot BESS</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>FIELD GERRARDS CROSS LTD</t>
+          <t>EDF Energy Customers Limited</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>E_GRCRB-1</t>
+          <t>E_BARNB-1</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -2834,26 +3282,28 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Gerrards Cross Sewage Treatment Works</t>
+          <t>Stairfoot Battery Storage Facility</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Peak Gen Power</t>
-        </is>
-      </c>
-      <c r="J39" t="n">
-        <v>20</v>
-      </c>
+          <t>Noriker Power Limited</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr">
         <is>
-          <t>Application Submitted</t>
-        </is>
-      </c>
-      <c r="L39" t="inlineStr"/>
+          <t>Operational</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>31/07/2021</t>
+        </is>
+      </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>SL9 7BE</t>
+          <t>S71 1HT</t>
         </is>
       </c>
       <c r="N39" t="inlineStr"/>
@@ -2862,30 +3312,46 @@
       <c r="Q39" t="inlineStr"/>
       <c r="R39" t="inlineStr"/>
       <c r="S39" t="inlineStr"/>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>verify</t>
+        </is>
+      </c>
+      <c r="U39" t="n">
+        <v>40</v>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>capacity_market</t>
+        </is>
+      </c>
+      <c r="W39" t="n">
+        <v>0.91</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>GB-BESS-FARNB</t>
+          <t>GB-BESS-ARNKB</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Farnham BESS</t>
+          <t>AR0006-BLOX</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Tesla Motors Limited</t>
+          <t>Octopus Energy Trading Limited</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>E_FARNB-1</t>
+          <t>E_ARNKB-1</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>20</v>
+        <v>41.7</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -2907,79 +3373,113 @@
       <c r="Q40" t="inlineStr"/>
       <c r="R40" t="inlineStr"/>
       <c r="S40" t="inlineStr"/>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>fill</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr"/>
+      <c r="V40" t="inlineStr"/>
+      <c r="W40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>GB-BESS-SWDNB</t>
+          <t>GB-BESS-FIDL</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Swindon</t>
+          <t>Fiddler's Ferry 2</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Conrad Energy (Trading) Ltd</t>
+          <t>Keadby Generation Limited</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>E_SWDNB-1</t>
+          <t>T_FIDL-2, T_FIDL-3, T_FIDL-4</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>19</v>
+        <v>41</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Distribution</t>
+          <t>Transmission</t>
         </is>
       </c>
       <c r="G41" t="b">
         <v>0</v>
       </c>
-      <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Fiddlers Ferry Power Station - Battery storage</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>SSE Enterprise (SSE PLC)</t>
+        </is>
+      </c>
+      <c r="J41" t="n">
+        <v>150</v>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Under Construction</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>WA5 2UT</t>
+        </is>
+      </c>
       <c r="N41" t="inlineStr"/>
       <c r="O41" t="inlineStr"/>
       <c r="P41" t="inlineStr"/>
       <c r="Q41" t="inlineStr"/>
       <c r="R41" t="inlineStr"/>
       <c r="S41" t="inlineStr"/>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>fill</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr"/>
+      <c r="V41" t="inlineStr"/>
+      <c r="W41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>GB-BESS-BROAB</t>
+          <t>GB-BESS-KEMB</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Broadditch Battery</t>
+          <t>Pivot Power Kemsley</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Tesla Motors Limited</t>
+          <t>EDF Energy Customers Limited</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>E_BROAB-1</t>
+          <t>T_KEMB-1</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>11</v>
+        <v>40.1</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Distribution</t>
+          <t>Transmission</t>
         </is>
       </c>
       <c r="G42" t="b">
@@ -2987,16 +3487,16 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Broadditch Battery Energy</t>
+          <t>Kemsley Substation</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Harmony Energy</t>
+          <t>Pivot Power</t>
         </is>
       </c>
       <c r="J42" t="n">
-        <v>11</v>
+        <v>49.9</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
@@ -3005,12 +3505,12 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>01/03/2023</t>
+          <t>25/10/2021</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>DA13 9PU</t>
+          <t>ME10 2</t>
         </is>
       </c>
       <c r="N42" t="inlineStr"/>
@@ -3019,30 +3519,38 @@
       <c r="Q42" t="inlineStr"/>
       <c r="R42" t="inlineStr"/>
       <c r="S42" t="inlineStr"/>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>fill</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr"/>
+      <c r="V42" t="inlineStr"/>
+      <c r="W42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>GB-BESS-TDRVE</t>
+          <t>GB-BESS-DALMB</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>The Drove</t>
+          <t>Dalmarnock_BESS</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Conrad Energy (Trading) Ltd</t>
+          <t>EDF Energy Customers Limited</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>E_TDRVE-1</t>
+          <t>E_DALMB-1</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3052,46 +3560,72 @@
       <c r="G43" t="b">
         <v>0</v>
       </c>
-      <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Dalmarnock Road - Battery Storage</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>EcoDev Group Limited</t>
+        </is>
+      </c>
+      <c r="J43" t="n">
+        <v>40</v>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Awaiting Construction</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>G73 1NY</t>
+        </is>
+      </c>
       <c r="N43" t="inlineStr"/>
       <c r="O43" t="inlineStr"/>
       <c r="P43" t="inlineStr"/>
       <c r="Q43" t="inlineStr"/>
       <c r="R43" t="inlineStr"/>
       <c r="S43" t="inlineStr"/>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>fill</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr"/>
+      <c r="V43" t="inlineStr"/>
+      <c r="W43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>GB-BESS-FIDL-3G</t>
+          <t>GB-BESS-SHILB</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Fiddler's Ferry GT 3</t>
+          <t>Shilton Lane BESS</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Keadby Generation Limited</t>
+          <t>Octopus Energy Trading Limited</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>T_FIDL-3G</t>
+          <t>E_SHILB-1</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Transmission</t>
+          <t>Distribution</t>
         </is>
       </c>
       <c r="G44" t="b">
@@ -3099,26 +3633,30 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Fiddlers Ferry Power Station - Battery storage</t>
+          <t>Land SW of Shilton Cottage</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>SSE Enterprise (SSE PLC)</t>
+          <t>Muirhall Energy</t>
         </is>
       </c>
       <c r="J44" t="n">
-        <v>150</v>
+        <v>29.9</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>Under Construction</t>
-        </is>
-      </c>
-      <c r="L44" t="inlineStr"/>
+          <t>Operational</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>01/01/2022</t>
+        </is>
+      </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>WA5 2UT</t>
+          <t>PA7 5BB</t>
         </is>
       </c>
       <c r="N44" t="inlineStr"/>
@@ -3127,30 +3665,38 @@
       <c r="Q44" t="inlineStr"/>
       <c r="R44" t="inlineStr"/>
       <c r="S44" t="inlineStr"/>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>fill</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr"/>
+      <c r="V44" t="inlineStr"/>
+      <c r="W44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>GB-BESS-WISHD</t>
+          <t>GB-BESS-TEBWB</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Wishaw Demand BMU</t>
+          <t>Tebworth BESS Power Park</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Zenobe Wishaw Limited</t>
+          <t>Arenko Cleantech Limited</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>T_WISHD-1</t>
+          <t>T_TEBWB-1</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1</v>
+        <v>39.9</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3162,30 +3708,24 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Wishaw Battery Storage Facility</t>
+          <t>Tebworth - Battery Storage</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Zenobe Energy</t>
-        </is>
-      </c>
-      <c r="J45" t="n">
-        <v>49.99</v>
-      </c>
+          <t>Sundon Green Limited</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr">
         <is>
-          <t>Operational</t>
-        </is>
-      </c>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>15/11/2023</t>
-        </is>
-      </c>
+          <t>Under Construction</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr">
         <is>
-          <t>ML2 0DP</t>
+          <t>LU7 9BP</t>
         </is>
       </c>
       <c r="N45" t="inlineStr"/>
@@ -3194,34 +3734,42 @@
       <c r="Q45" t="inlineStr"/>
       <c r="R45" t="inlineStr"/>
       <c r="S45" t="inlineStr"/>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>fill</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr"/>
+      <c r="V45" t="inlineStr"/>
+      <c r="W45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>GB-BESS-FIDL-2G</t>
+          <t>GB-BESS-POTES</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Fiddler's Ferry GT2</t>
+          <t>Port of Tyne Energy Storage</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Keadby Generation Limited</t>
+          <t>Arenko Cleantech Limited</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>T_FIDL-2G</t>
+          <t>E_POTES-1</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Transmission</t>
+          <t>Distribution</t>
         </is>
       </c>
       <c r="G46" t="b">
@@ -3229,26 +3777,30 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Fiddlers Ferry Power Station - Battery storage</t>
+          <t>Port of Tyne</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>SSE Enterprise (SSE PLC)</t>
+          <t>Foresight</t>
         </is>
       </c>
       <c r="J46" t="n">
-        <v>150</v>
+        <v>35</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>Under Construction</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr"/>
+          <t>Operational</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>01/07/2018</t>
+        </is>
+      </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>WA5 2UT</t>
+          <t>NE34 9PT</t>
         </is>
       </c>
       <c r="N46" t="inlineStr"/>
@@ -3257,6 +3809,1261 @@
       <c r="Q46" t="inlineStr"/>
       <c r="R46" t="inlineStr"/>
       <c r="S46" t="inlineStr"/>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>fill</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr"/>
+      <c r="V46" t="inlineStr"/>
+      <c r="W46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>GB-BESS-ARBRB</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Arbroath Battery Storage</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Octopus Energy Trading Limited</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>E_ARBRB-1</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>34.5</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Distribution</t>
+        </is>
+      </c>
+      <c r="G47" t="b">
+        <v>0</v>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Arbroath Battery Storage</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Coronation Power / Persimmon Homes</t>
+        </is>
+      </c>
+      <c r="J47" t="n">
+        <v>35</v>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Operational</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>02/04/2024</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>DD11 3ET</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
+      <c r="O47" t="inlineStr"/>
+      <c r="P47" t="inlineStr"/>
+      <c r="Q47" t="inlineStr"/>
+      <c r="R47" t="inlineStr"/>
+      <c r="S47" t="inlineStr"/>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>fill</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr"/>
+      <c r="V47" t="inlineStr"/>
+      <c r="W47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>GB-BESS-NTAWB</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>North Tawton BESS</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>EDF Energy Customers Limited</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>E_NTAWB-1</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>32</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Distribution</t>
+        </is>
+      </c>
+      <c r="G48" t="b">
+        <v>0</v>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>North Tawton Primary Substation - Battery Storage</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Balance Power Projects Limited</t>
+        </is>
+      </c>
+      <c r="J48" t="n">
+        <v>30</v>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Awaiting Construction</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>EX20 2DA</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
+      <c r="O48" t="inlineStr"/>
+      <c r="P48" t="inlineStr"/>
+      <c r="Q48" t="inlineStr"/>
+      <c r="R48" t="inlineStr"/>
+      <c r="S48" t="inlineStr"/>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>verify</t>
+        </is>
+      </c>
+      <c r="U48" t="n">
+        <v>30</v>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>capacity_market</t>
+        </is>
+      </c>
+      <c r="W48" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>GB-BESS-ERSKB</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Erskine BESS</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>EDF Energy Customers Limited</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>E_ERSKB-1</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Distribution</t>
+        </is>
+      </c>
+      <c r="G49" t="b">
+        <v>0</v>
+      </c>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
+      <c r="O49" t="inlineStr"/>
+      <c r="P49" t="inlineStr"/>
+      <c r="Q49" t="inlineStr"/>
+      <c r="R49" t="inlineStr"/>
+      <c r="S49" t="inlineStr"/>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>verify</t>
+        </is>
+      </c>
+      <c r="U49" t="n">
+        <v>30</v>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>capacity_market</t>
+        </is>
+      </c>
+      <c r="W49" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>GB-BESS-BLKPB</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Blackpool</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Conrad Energy (Trading) Ltd</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>E_BLKPB-1</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Distribution</t>
+        </is>
+      </c>
+      <c r="G50" t="b">
+        <v>0</v>
+      </c>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
+      <c r="O50" t="inlineStr"/>
+      <c r="P50" t="inlineStr"/>
+      <c r="Q50" t="inlineStr"/>
+      <c r="R50" t="inlineStr"/>
+      <c r="S50" t="inlineStr"/>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>fill</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr"/>
+      <c r="V50" t="inlineStr"/>
+      <c r="W50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>GB-BESS-WHTBB</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Whitebirk BESS</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Field Whitebirk Ltd</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>E_WHTBB-1</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>25</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Distribution</t>
+        </is>
+      </c>
+      <c r="G51" t="b">
+        <v>0</v>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Davies Road - Whitebirk Battery Storage</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="J51" t="n">
+        <v>25</v>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Awaiting Construction</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>BB1 3HR</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
+      <c r="O51" t="inlineStr"/>
+      <c r="P51" t="inlineStr"/>
+      <c r="Q51" t="inlineStr"/>
+      <c r="R51" t="inlineStr"/>
+      <c r="S51" t="inlineStr"/>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>verify</t>
+        </is>
+      </c>
+      <c r="U51" t="n">
+        <v>36.6</v>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>capacity_market</t>
+        </is>
+      </c>
+      <c r="W51" t="n">
+        <v>1.47</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>GB-BESS-TORQB</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Torquay</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Conrad Energy (Trading) Ltd</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>E_TORQB-1</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Distribution</t>
+        </is>
+      </c>
+      <c r="G52" t="b">
+        <v>0</v>
+      </c>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
+      <c r="O52" t="inlineStr"/>
+      <c r="P52" t="inlineStr"/>
+      <c r="Q52" t="inlineStr"/>
+      <c r="R52" t="inlineStr"/>
+      <c r="S52" t="inlineStr"/>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>fill</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr"/>
+      <c r="V52" t="inlineStr"/>
+      <c r="W52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>GB-BESS-PNYCB</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Pen y Cymoedd Battery</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Arenko Cleantech Limited</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>T_PNYCB-1</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>22</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Transmission</t>
+        </is>
+      </c>
+      <c r="G53" t="b">
+        <v>0</v>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Pen y Cymoedd Energy Storage</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Vattenfall</t>
+        </is>
+      </c>
+      <c r="J53" t="n">
+        <v>22</v>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Operational</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>01/05/2018</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>SA13 3HF</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
+      <c r="O53" t="inlineStr"/>
+      <c r="P53" t="inlineStr"/>
+      <c r="Q53" t="inlineStr"/>
+      <c r="R53" t="inlineStr"/>
+      <c r="S53" t="inlineStr"/>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>fill</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr"/>
+      <c r="V53" t="inlineStr"/>
+      <c r="W53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>GB-BESS-NEWPB</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Newport BESS</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Field Newport Ltd</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>E_NEWPB-1</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Distribution</t>
+        </is>
+      </c>
+      <c r="G54" t="b">
+        <v>0</v>
+      </c>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
+      <c r="O54" t="inlineStr"/>
+      <c r="P54" t="inlineStr"/>
+      <c r="Q54" t="inlineStr"/>
+      <c r="R54" t="inlineStr"/>
+      <c r="S54" t="inlineStr"/>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>fill</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr"/>
+      <c r="V54" t="inlineStr"/>
+      <c r="W54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>GB-BESS-OLDHB</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Oldham BESS</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Field Oldham Ltd</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>E_OLDHB-1</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>20</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Distribution</t>
+        </is>
+      </c>
+      <c r="G55" t="b">
+        <v>0</v>
+      </c>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
+      <c r="O55" t="inlineStr"/>
+      <c r="P55" t="inlineStr"/>
+      <c r="Q55" t="inlineStr"/>
+      <c r="R55" t="inlineStr"/>
+      <c r="S55" t="inlineStr"/>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>verify</t>
+        </is>
+      </c>
+      <c r="U55" t="n">
+        <v>20</v>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>capacity_market</t>
+        </is>
+      </c>
+      <c r="W55" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>GB-BESS-HAWKB</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>HawkersHill  Battery</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Tesla Motors Limited</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>E_HAWKB-1</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>20</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Distribution</t>
+        </is>
+      </c>
+      <c r="G56" t="b">
+        <v>0</v>
+      </c>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
+      <c r="O56" t="inlineStr"/>
+      <c r="P56" t="inlineStr"/>
+      <c r="Q56" t="inlineStr"/>
+      <c r="R56" t="inlineStr"/>
+      <c r="S56" t="inlineStr"/>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>fill</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr"/>
+      <c r="V56" t="inlineStr"/>
+      <c r="W56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>GB-BESS-GRCRB</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Gerrards Cross BESS</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>FIELD GERRARDS CROSS LTD</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>E_GRCRB-1</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>20</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Distribution</t>
+        </is>
+      </c>
+      <c r="G57" t="b">
+        <v>0</v>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Gerrards Cross Sewage Treatment Works</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Peak Gen Power</t>
+        </is>
+      </c>
+      <c r="J57" t="n">
+        <v>20</v>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Application Submitted</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>SL9 7BE</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
+      <c r="O57" t="inlineStr"/>
+      <c r="P57" t="inlineStr"/>
+      <c r="Q57" t="inlineStr"/>
+      <c r="R57" t="inlineStr"/>
+      <c r="S57" t="inlineStr"/>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>fill</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr"/>
+      <c r="V57" t="inlineStr"/>
+      <c r="W57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>GB-BESS-FARNB</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Farnham BESS</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Tesla Motors Limited</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>E_FARNB-1</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>20</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Distribution</t>
+        </is>
+      </c>
+      <c r="G58" t="b">
+        <v>0</v>
+      </c>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
+      <c r="O58" t="inlineStr"/>
+      <c r="P58" t="inlineStr"/>
+      <c r="Q58" t="inlineStr"/>
+      <c r="R58" t="inlineStr"/>
+      <c r="S58" t="inlineStr"/>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>fill</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr"/>
+      <c r="V58" t="inlineStr"/>
+      <c r="W58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>GB-BESS-SWDNB</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Swindon</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Conrad Energy (Trading) Ltd</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>E_SWDNB-1</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>19</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Distribution</t>
+        </is>
+      </c>
+      <c r="G59" t="b">
+        <v>0</v>
+      </c>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
+      <c r="O59" t="inlineStr"/>
+      <c r="P59" t="inlineStr"/>
+      <c r="Q59" t="inlineStr"/>
+      <c r="R59" t="inlineStr"/>
+      <c r="S59" t="inlineStr"/>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>fill</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr"/>
+      <c r="V59" t="inlineStr"/>
+      <c r="W59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>GB-BESS-BROAB</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Broadditch Battery</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Tesla Motors Limited</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>E_BROAB-1</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>11</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Distribution</t>
+        </is>
+      </c>
+      <c r="G60" t="b">
+        <v>0</v>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Broadditch Battery Energy</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Harmony Energy</t>
+        </is>
+      </c>
+      <c r="J60" t="n">
+        <v>11</v>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Operational</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>01/03/2023</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>DA13 9PU</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr"/>
+      <c r="O60" t="inlineStr"/>
+      <c r="P60" t="inlineStr"/>
+      <c r="Q60" t="inlineStr"/>
+      <c r="R60" t="inlineStr"/>
+      <c r="S60" t="inlineStr"/>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>fill</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr"/>
+      <c r="V60" t="inlineStr"/>
+      <c r="W60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>GB-BESS-BHOLB</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Holes Bay Battery</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Tesla Motors Limited</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>E_BHOLB-1</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Distribution</t>
+        </is>
+      </c>
+      <c r="G61" t="b">
+        <v>0</v>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Holes Bay</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Harmony Energy</t>
+        </is>
+      </c>
+      <c r="J61" t="n">
+        <v>15</v>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Operational</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>01/06/2020</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>BH15 2AL</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr"/>
+      <c r="O61" t="inlineStr"/>
+      <c r="P61" t="inlineStr"/>
+      <c r="Q61" t="inlineStr"/>
+      <c r="R61" t="inlineStr"/>
+      <c r="S61" t="inlineStr"/>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>verify</t>
+        </is>
+      </c>
+      <c r="U61" t="n">
+        <v>10</v>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>capacity_market</t>
+        </is>
+      </c>
+      <c r="W61" t="n">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>GB-BESS-TDRVE</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>The Drove</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Conrad Energy (Trading) Ltd</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>E_TDRVE-1</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>6</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Distribution</t>
+        </is>
+      </c>
+      <c r="G62" t="b">
+        <v>0</v>
+      </c>
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
+      <c r="O62" t="inlineStr"/>
+      <c r="P62" t="inlineStr"/>
+      <c r="Q62" t="inlineStr"/>
+      <c r="R62" t="inlineStr"/>
+      <c r="S62" t="inlineStr"/>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>fill</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr"/>
+      <c r="V62" t="inlineStr"/>
+      <c r="W62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>GB-BESS-FIDL-3G</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Fiddler's Ferry GT 3</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Keadby Generation Limited</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>T_FIDL-3G</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>1</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Transmission</t>
+        </is>
+      </c>
+      <c r="G63" t="b">
+        <v>0</v>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Fiddlers Ferry Power Station - Battery storage</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>SSE Enterprise (SSE PLC)</t>
+        </is>
+      </c>
+      <c r="J63" t="n">
+        <v>150</v>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Under Construction</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>WA5 2UT</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr"/>
+      <c r="O63" t="inlineStr"/>
+      <c r="P63" t="inlineStr"/>
+      <c r="Q63" t="inlineStr"/>
+      <c r="R63" t="inlineStr"/>
+      <c r="S63" t="inlineStr"/>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>fill</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr"/>
+      <c r="V63" t="inlineStr"/>
+      <c r="W63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>GB-BESS-WISHD</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Wishaw Demand BMU</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Zenobe Wishaw Limited</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>T_WISHD-1</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>1</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Transmission</t>
+        </is>
+      </c>
+      <c r="G64" t="b">
+        <v>0</v>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Wishaw Battery Storage Facility</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>Zenobe Energy</t>
+        </is>
+      </c>
+      <c r="J64" t="n">
+        <v>49.99</v>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Operational</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>15/11/2023</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>ML2 0DP</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr"/>
+      <c r="O64" t="inlineStr"/>
+      <c r="P64" t="inlineStr"/>
+      <c r="Q64" t="inlineStr"/>
+      <c r="R64" t="inlineStr"/>
+      <c r="S64" t="inlineStr"/>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>fill</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr"/>
+      <c r="V64" t="inlineStr"/>
+      <c r="W64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>GB-BESS-FIDL-2G</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Fiddler's Ferry GT2</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Keadby Generation Limited</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>T_FIDL-2G</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>1</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Transmission</t>
+        </is>
+      </c>
+      <c r="G65" t="b">
+        <v>0</v>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Fiddlers Ferry Power Station - Battery storage</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>SSE Enterprise (SSE PLC)</t>
+        </is>
+      </c>
+      <c r="J65" t="n">
+        <v>150</v>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Under Construction</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>WA5 2UT</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr"/>
+      <c r="O65" t="inlineStr"/>
+      <c r="P65" t="inlineStr"/>
+      <c r="Q65" t="inlineStr"/>
+      <c r="R65" t="inlineStr"/>
+      <c r="S65" t="inlineStr"/>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>fill</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr"/>
+      <c r="V65" t="inlineStr"/>
+      <c r="W65" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/reference/battery_energy_capacity.xlsx
+++ b/data/reference/battery_energy_capacity.xlsx
@@ -3367,12 +3367,32 @@
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
-      <c r="O40" t="inlineStr"/>
-      <c r="P40" t="inlineStr"/>
-      <c r="Q40" t="inlineStr"/>
-      <c r="R40" t="inlineStr"/>
-      <c r="S40" t="inlineStr"/>
+      <c r="N40" t="n">
+        <v>47</v>
+      </c>
+      <c r="O40" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>corporate</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>https://www.greshamhouse.com/</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>Gresham House Energy Storage Fund half-year results (Bloxwich)</t>
+        </is>
+      </c>
       <c r="T40" t="inlineStr">
         <is>
           <t>fill</t>
@@ -4278,12 +4298,32 @@
           <t>SA13 3HF</t>
         </is>
       </c>
-      <c r="N53" t="inlineStr"/>
-      <c r="O53" t="inlineStr"/>
-      <c r="P53" t="inlineStr"/>
-      <c r="Q53" t="inlineStr"/>
-      <c r="R53" t="inlineStr"/>
-      <c r="S53" t="inlineStr"/>
+      <c r="N53" t="n">
+        <v>16</v>
+      </c>
+      <c r="O53" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>corporate</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>https://group.vattenfall.com/</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>Vattenfall co-located wind + BESS operations data</t>
+        </is>
+      </c>
       <c r="T53" t="inlineStr">
         <is>
           <t>fill</t>
@@ -4445,12 +4485,32 @@
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
-      <c r="O56" t="inlineStr"/>
-      <c r="P56" t="inlineStr"/>
-      <c r="Q56" t="inlineStr"/>
-      <c r="R56" t="inlineStr"/>
-      <c r="S56" t="inlineStr"/>
+      <c r="N56" t="n">
+        <v>40</v>
+      </c>
+      <c r="O56" t="n">
+        <v>2</v>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>corporate</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>https://tagenergy.com/</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>TagEnergy / Tesla Megapack press release</t>
+        </is>
+      </c>
       <c r="T56" t="inlineStr">
         <is>
           <t>fill</t>
@@ -4516,12 +4576,32 @@
           <t>SL9 7BE</t>
         </is>
       </c>
-      <c r="N57" t="inlineStr"/>
-      <c r="O57" t="inlineStr"/>
-      <c r="P57" t="inlineStr"/>
-      <c r="Q57" t="inlineStr"/>
-      <c r="R57" t="inlineStr"/>
-      <c r="S57" t="inlineStr"/>
+      <c r="N57" t="n">
+        <v>20</v>
+      </c>
+      <c r="O57" t="n">
+        <v>1</v>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>corporate</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>https://field.energy/</t>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>Field operational portfolio disclosures</t>
+        </is>
+      </c>
       <c r="T57" t="inlineStr">
         <is>
           <t>fill</t>
@@ -4569,12 +4649,32 @@
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
-      <c r="O58" t="inlineStr"/>
-      <c r="P58" t="inlineStr"/>
-      <c r="Q58" t="inlineStr"/>
-      <c r="R58" t="inlineStr"/>
-      <c r="S58" t="inlineStr"/>
+      <c r="N58" t="n">
+        <v>40</v>
+      </c>
+      <c r="O58" t="n">
+        <v>2</v>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>corporate</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>https://www.harmonyenergyincometrust.com/</t>
+        </is>
+      </c>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>Harmony Energy Income Trust energisation report</t>
+        </is>
+      </c>
       <c r="T58" t="inlineStr">
         <is>
           <t>fill</t>

--- a/data/reference/battery_energy_capacity.xlsx
+++ b/data/reference/battery_energy_capacity.xlsx
@@ -1182,7 +1182,7 @@
         <v>310</v>
       </c>
       <c r="O9" t="n">
-        <v>2.4</v>
+        <v>5.5</v>
       </c>
       <c r="P9" t="inlineStr">
         <is>
@@ -1201,7 +1201,7 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>Envision &amp; Pulse Clean Energy</t>
+          <t>Envision &amp; Pulse Clean Energy. NEEDS REVIEW: implies 129 MW project vs 56 MW BM Unit</t>
         </is>
       </c>
       <c r="T9" t="inlineStr"/>
@@ -1964,12 +1964,32 @@
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
-      <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr"/>
-      <c r="R19" t="inlineStr"/>
-      <c r="S19" t="inlineStr"/>
+      <c r="N19" t="n">
+        <v>49</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>corporate</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>https://www.edfenergy.com/</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>EDF Energy; EFR-era short duration</t>
+        </is>
+      </c>
       <c r="T19" t="inlineStr">
         <is>
           <t>fill</t>
@@ -2017,12 +2037,32 @@
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
-      <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="inlineStr"/>
-      <c r="R20" t="inlineStr"/>
-      <c r="S20" t="inlineStr"/>
+      <c r="N20" t="n">
+        <v>165</v>
+      </c>
+      <c r="O20" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>corporate</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>https://constantineenergystorage.com/</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>Constantine 'Golds Hill/Ocker Hill'; standard 57MW/165MWh block</t>
+        </is>
+      </c>
       <c r="T20" t="inlineStr">
         <is>
           <t>fill</t>
@@ -2088,12 +2128,32 @@
           <t>OL9 9XA</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr"/>
-      <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="inlineStr"/>
-      <c r="R21" t="inlineStr"/>
-      <c r="S21" t="inlineStr"/>
+      <c r="N21" t="n">
+        <v>165</v>
+      </c>
+      <c r="O21" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>corporate</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>https://constantineenergystorage.com/</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>Constantine portfolio; standard block. Supersedes CM 114 MWh</t>
+        </is>
+      </c>
       <c r="T21" t="inlineStr">
         <is>
           <t>verify</t>
@@ -2167,12 +2227,32 @@
           <t>LS25 5LD</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr"/>
-      <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr"/>
-      <c r="R22" t="inlineStr"/>
-      <c r="S22" t="inlineStr"/>
+      <c r="N22" t="n">
+        <v>165</v>
+      </c>
+      <c r="O22" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>corporate</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>https://constantineenergystorage.com/</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>Pelagic / Constantine portfolio; standard block</t>
+        </is>
+      </c>
       <c r="T22" t="inlineStr">
         <is>
           <t>fill</t>
@@ -2238,12 +2318,32 @@
           <t>CH1 6EH</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr"/>
-      <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="inlineStr"/>
-      <c r="R23" t="inlineStr"/>
-      <c r="S23" t="inlineStr"/>
+      <c r="N23" t="n">
+        <v>165</v>
+      </c>
+      <c r="O23" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>corporate</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>https://constantineenergystorage.com/</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>Constantine portfolio; standard block</t>
+        </is>
+      </c>
       <c r="T23" t="inlineStr">
         <is>
           <t>fill</t>
